--- a/trades.xlsx
+++ b/trades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\trading-journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC8CBCEC-2993-46C9-B22D-E0ECBB1BEB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA7051F-910B-4536-9ECC-636E111DD284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>17</v>
@@ -625,7 +625,7 @@
         <v>21</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>

--- a/trades.xlsx
+++ b/trades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\trading-journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA7051F-910B-4536-9ECC-636E111DD284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1046DD37-3BE4-454E-8CB6-5F417B5BE346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,28 @@
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -210,6 +232,70 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -600,7 +686,9 @@
       <c r="I4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="7"/>
+      <c r="J4" s="7" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="4">

--- a/trades.xlsx
+++ b/trades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\trading-journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1046DD37-3BE4-454E-8CB6-5F417B5BE346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F81D0EED-FFB4-471E-B449-DBDFA1538B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,30 +19,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
   <si>
     <t>Trading Journal - Trade Log</t>
   </si>
@@ -133,6 +111,9 @@
   <si>
     <t>Moved SL to BEEE</t>
   </si>
+  <si>
+    <t>https://www.tradingview.com/x/j2XJvs6h/</t>
+  </si>
 </sst>
 </file>
 
@@ -142,7 +123,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="hh:mm"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -172,6 +153,14 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -195,10 +184,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -217,8 +207,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -232,70 +226,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -613,7 +543,7 @@
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
-    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="10" max="10" width="38.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.4">
@@ -686,8 +616,8 @@
       <c r="I4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="7" t="e" vm="1">
-        <v>#VALUE!</v>
+      <c r="J4" s="8" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -12725,9 +12655,12 @@
       <formula1>"TP,SL,BE"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="J4" r:id="rId1" xr:uid="{886DD11E-A6A7-4084-8D9A-25624006ECAD}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/trades.xlsx
+++ b/trades.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\trading-journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F81D0EED-FFB4-471E-B449-DBDFA1538B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{159FE17D-04B2-424A-B7ED-1A671B1D1DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="86280" yWindow="-5520" windowWidth="16440" windowHeight="29040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trade Log" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="32">
   <si>
     <t>Trading Journal - Trade Log</t>
   </si>
@@ -113,6 +126,9 @@
   </si>
   <si>
     <t>https://www.tradingview.com/x/j2XJvs6h/</t>
+  </si>
+  <si>
+    <t>Trendline</t>
   </si>
 </sst>
 </file>
@@ -229,8 +245,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TradeLog" displayName="TradeLog" ref="A3:J1000">
-  <autoFilter ref="A3:J1000" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TradeLog" displayName="TradeLog" ref="A3:J999">
+  <autoFilter ref="A3:J999" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Trade No"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Date"/>
@@ -532,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J1000"/>
+  <dimension ref="A1:J999"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -737,195 +753,387 @@
       <c r="J8" s="7"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
-      <c r="B9" s="5"/>
+      <c r="A9" s="4">
+        <v>6</v>
+      </c>
+      <c r="B9" s="5">
+        <v>43839</v>
+      </c>
       <c r="C9" s="6"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
+      <c r="D9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="7"/>
+      <c r="H9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="4"/>
-      <c r="B10" s="5"/>
+      <c r="A10" s="4">
+        <v>7</v>
+      </c>
+      <c r="B10" s="5">
+        <v>43844</v>
+      </c>
       <c r="C10" s="6"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
+      <c r="D10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="7"/>
+      <c r="H10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="J10" s="7"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
-      <c r="B11" s="5"/>
+      <c r="A11" s="4">
+        <v>8</v>
+      </c>
+      <c r="B11" s="5">
+        <v>43854</v>
+      </c>
       <c r="C11" s="6"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
+      <c r="D11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="7"/>
+      <c r="H11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="J11" s="7"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="4"/>
-      <c r="B12" s="5"/>
+      <c r="A12" s="4">
+        <v>9</v>
+      </c>
+      <c r="B12" s="5">
+        <v>43854</v>
+      </c>
       <c r="C12" s="6"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
+      <c r="D12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="7"/>
+      <c r="H12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="J12" s="7"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="4"/>
-      <c r="B13" s="5"/>
+      <c r="A13" s="4">
+        <v>10</v>
+      </c>
+      <c r="B13" s="5">
+        <v>43860</v>
+      </c>
       <c r="C13" s="6"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
+      <c r="D13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="7"/>
+      <c r="H13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="J13" s="7"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="4"/>
-      <c r="B14" s="5"/>
+      <c r="A14" s="4">
+        <v>11</v>
+      </c>
+      <c r="B14" s="5">
+        <v>43879</v>
+      </c>
       <c r="C14" s="6"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
+      <c r="D14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="7"/>
+      <c r="H14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="J14" s="7"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="4"/>
-      <c r="B15" s="5"/>
+      <c r="A15" s="4">
+        <v>12</v>
+      </c>
+      <c r="B15" s="5">
+        <v>43900</v>
+      </c>
       <c r="C15" s="6"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
+      <c r="D15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="7"/>
+      <c r="H15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="J15" s="7"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="4"/>
-      <c r="B16" s="5"/>
+      <c r="A16" s="4">
+        <v>13</v>
+      </c>
+      <c r="B16" s="5">
+        <v>43915</v>
+      </c>
       <c r="C16" s="6"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
+      <c r="D16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="7"/>
+      <c r="H16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="J16" s="7"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="4"/>
-      <c r="B17" s="5"/>
+      <c r="A17" s="4">
+        <v>14</v>
+      </c>
+      <c r="B17" s="5">
+        <v>43923</v>
+      </c>
       <c r="C17" s="6"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
+      <c r="D17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="7"/>
+      <c r="H17" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="J17" s="7"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="4"/>
-      <c r="B18" s="5"/>
+      <c r="A18" s="4">
+        <v>15</v>
+      </c>
+      <c r="B18" s="5">
+        <v>43935</v>
+      </c>
       <c r="C18" s="6"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
+      <c r="D18" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="7"/>
+      <c r="H18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="J18" s="7"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="5"/>
+      <c r="A19" s="4">
+        <v>16</v>
+      </c>
+      <c r="B19" s="5">
+        <v>43943</v>
+      </c>
       <c r="C19" s="6"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
+      <c r="D19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="7"/>
+      <c r="H19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="J19" s="7"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="4"/>
-      <c r="B20" s="5"/>
+      <c r="A20" s="4">
+        <v>17</v>
+      </c>
+      <c r="B20" s="5">
+        <v>43955</v>
+      </c>
       <c r="C20" s="6"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
+      <c r="D20" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="7"/>
+      <c r="H20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="J20" s="7"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="4"/>
-      <c r="B21" s="5"/>
+      <c r="A21" s="4">
+        <v>18</v>
+      </c>
+      <c r="B21" s="5">
+        <v>43957</v>
+      </c>
       <c r="C21" s="6"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
+      <c r="D21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="7"/>
+      <c r="H21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="J21" s="7"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="4"/>
-      <c r="B22" s="5"/>
+      <c r="A22" s="4">
+        <v>19</v>
+      </c>
+      <c r="B22" s="5">
+        <v>43957</v>
+      </c>
       <c r="C22" s="6"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
+      <c r="D22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="7"/>
+      <c r="H22" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="J22" s="7"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="4"/>
-      <c r="B23" s="5"/>
+      <c r="A23" s="4">
+        <v>20</v>
+      </c>
+      <c r="B23" s="5">
+        <v>43972</v>
+      </c>
       <c r="C23" s="6"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
+      <c r="D23" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="7"/>
+      <c r="H23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="J23" s="7"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="4"/>
-      <c r="B24" s="5"/>
+      <c r="A24" s="4">
+        <v>21</v>
+      </c>
+      <c r="B24" s="5">
+        <v>43980</v>
+      </c>
       <c r="C24" s="6"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
+      <c r="D24" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="7"/>
+      <c r="H24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="J24" s="7"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
@@ -12628,30 +12836,18 @@
       <c r="I999" s="7"/>
       <c r="J999" s="7"/>
     </row>
-    <row r="1000" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1000" s="4"/>
-      <c r="B1000" s="5"/>
-      <c r="C1000" s="6"/>
-      <c r="D1000" s="4"/>
-      <c r="E1000" s="4"/>
-      <c r="F1000" s="4"/>
-      <c r="G1000" s="4"/>
-      <c r="H1000" s="4"/>
-      <c r="I1000" s="7"/>
-      <c r="J1000" s="7"/>
-    </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="Pick a market (edit this list under Data &gt; Data Validation to add more)." sqref="D4:D1000" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="Pick a market (edit this list under Data &gt; Data Validation to add more)." sqref="D4:D999" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"XAUUSD,ETHUSD,GBPUSD"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="BUY or SELL." sqref="E4:E1000" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="BUY or SELL." sqref="E4:E999" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"BUY,SELL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="Pick a session." sqref="F4:F1000" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="Pick a session." sqref="F4:F999" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Asia,London,New York"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="TP, SL or BE." sqref="H4:H1000" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="TP, SL or BE." sqref="H4:H999" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"TP,SL,BE"</formula1>
     </dataValidation>
   </dataValidations>

--- a/trades.xlsx
+++ b/trades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\trading-journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{159FE17D-04B2-424A-B7ED-1A671B1D1DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{724141F5-5EF1-4A3D-B8DA-1E82EDCB0DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="86280" yWindow="-5520" windowWidth="16440" windowHeight="29040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="37">
   <si>
     <t>Trading Journal - Trade Log</t>
   </si>
@@ -129,6 +129,21 @@
   </si>
   <si>
     <t>Trendline</t>
+  </si>
+  <si>
+    <t>https://thefreechart.com/x/IHfqwma2/</t>
+  </si>
+  <si>
+    <t>https://thefreechart.com/x/TUSkov8F/</t>
+  </si>
+  <si>
+    <t>https://thefreechart.com/x/arJlViGf/</t>
+  </si>
+  <si>
+    <t>https://thefreechart.com/x/rDDz4pUh/</t>
+  </si>
+  <si>
+    <t>https://thefreechart.com/x/UxZXxJr9/</t>
   </si>
 </sst>
 </file>
@@ -1137,172 +1152,368 @@
       <c r="J24" s="7"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="4"/>
-      <c r="B25" s="5"/>
+      <c r="A25" s="4">
+        <v>22</v>
+      </c>
+      <c r="B25" s="5">
+        <v>44036</v>
+      </c>
       <c r="C25" s="6"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
+      <c r="D25" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
+      <c r="H25" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="4"/>
-      <c r="B26" s="5"/>
+      <c r="A26" s="4">
+        <v>23</v>
+      </c>
+      <c r="B26" s="5">
+        <v>44053</v>
+      </c>
       <c r="C26" s="6"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
+      <c r="D26" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
+      <c r="H26" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="4"/>
-      <c r="B27" s="5"/>
+      <c r="A27" s="4">
+        <v>24</v>
+      </c>
+      <c r="B27" s="5">
+        <v>44061</v>
+      </c>
       <c r="C27" s="6"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
+      <c r="D27" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
+      <c r="H27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="4"/>
-      <c r="B28" s="5"/>
+      <c r="A28" s="4">
+        <v>25</v>
+      </c>
+      <c r="B28" s="5">
+        <v>44076</v>
+      </c>
       <c r="C28" s="6"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
+      <c r="D28" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
+      <c r="H28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="4"/>
-      <c r="B29" s="5"/>
+      <c r="A29" s="4">
+        <v>26</v>
+      </c>
+      <c r="B29" s="5">
+        <v>44082</v>
+      </c>
       <c r="C29" s="6"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
+      <c r="D29" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
+      <c r="H29" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="4"/>
-      <c r="B30" s="5"/>
+      <c r="A30" s="4">
+        <v>27</v>
+      </c>
+      <c r="B30" s="5">
+        <v>44109</v>
+      </c>
       <c r="C30" s="6"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
+      <c r="D30" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
+      <c r="H30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="4"/>
-      <c r="B31" s="5"/>
+      <c r="A31" s="4">
+        <v>28</v>
+      </c>
+      <c r="B31" s="5">
+        <v>44138</v>
+      </c>
       <c r="C31" s="6"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
+      <c r="D31" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
+      <c r="H31" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="4"/>
-      <c r="B32" s="5"/>
+      <c r="A32" s="4">
+        <v>29</v>
+      </c>
+      <c r="B32" s="5">
+        <v>44140</v>
+      </c>
       <c r="C32" s="6"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
+      <c r="D32" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
+      <c r="H32" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="4"/>
-      <c r="B33" s="5"/>
+      <c r="A33" s="4">
+        <v>30</v>
+      </c>
+      <c r="B33" s="5">
+        <v>44158</v>
+      </c>
       <c r="C33" s="6"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
+      <c r="D33" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
+      <c r="H33" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="4"/>
-      <c r="B34" s="5"/>
+      <c r="A34" s="4">
+        <v>31</v>
+      </c>
+      <c r="B34" s="5">
+        <v>44167</v>
+      </c>
       <c r="C34" s="6"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
+      <c r="D34" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="7"/>
+      <c r="H34" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="4"/>
-      <c r="B35" s="5"/>
+      <c r="A35" s="4">
+        <v>32</v>
+      </c>
+      <c r="B35" s="5">
+        <v>44175</v>
+      </c>
       <c r="C35" s="6"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
+      <c r="D35" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="7"/>
+      <c r="H35" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="4"/>
-      <c r="B36" s="5"/>
+      <c r="A36" s="4">
+        <v>33</v>
+      </c>
+      <c r="B36" s="5">
+        <v>44176</v>
+      </c>
       <c r="C36" s="6"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
+      <c r="D36" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="7"/>
-      <c r="J36" s="7"/>
+      <c r="H36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="4"/>
-      <c r="B37" s="5"/>
+      <c r="A37" s="4">
+        <v>34</v>
+      </c>
+      <c r="B37" s="5">
+        <v>44188</v>
+      </c>
       <c r="C37" s="6"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
+      <c r="D37" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="7"/>
+      <c r="H37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="4"/>
-      <c r="B38" s="5"/>
+      <c r="A38" s="4">
+        <v>35</v>
+      </c>
+      <c r="B38" s="5">
+        <v>44193</v>
+      </c>
       <c r="C38" s="6"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
+      <c r="D38" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
+      <c r="H38" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
@@ -12853,10 +13064,24 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="J4" r:id="rId1" xr:uid="{886DD11E-A6A7-4084-8D9A-25624006ECAD}"/>
+    <hyperlink ref="J38" r:id="rId2" xr:uid="{623704F0-0601-4D2E-A751-8060B75B0D88}"/>
+    <hyperlink ref="J37" r:id="rId3" xr:uid="{91095999-FCFE-46CD-B204-6103E44B467A}"/>
+    <hyperlink ref="J36" r:id="rId4" xr:uid="{972561D1-305A-4282-A7B4-FCEDA6CFBF4F}"/>
+    <hyperlink ref="J35" r:id="rId5" xr:uid="{89A5A8BD-98C5-41AF-829C-BB1D611A1AFF}"/>
+    <hyperlink ref="J34" r:id="rId6" xr:uid="{4099F7B4-F6F2-4CB9-B096-97CB8EFC661F}"/>
+    <hyperlink ref="J33" r:id="rId7" xr:uid="{7027DC13-E5A1-49BC-9EDB-3D001113E112}"/>
+    <hyperlink ref="J32" r:id="rId8" xr:uid="{F4BCD004-CDAF-4893-8E1B-4834F72BDEC6}"/>
+    <hyperlink ref="J31" r:id="rId9" xr:uid="{D10218F1-074C-41F2-874F-0D6B2E299E04}"/>
+    <hyperlink ref="J30" r:id="rId10" xr:uid="{E5D9EFF4-0438-47AC-9448-8896FE8352C0}"/>
+    <hyperlink ref="J29" r:id="rId11" xr:uid="{78E4062F-AB6A-4DBD-BEC8-6C5101CCCBCF}"/>
+    <hyperlink ref="J28" r:id="rId12" xr:uid="{A2B82276-3248-4BBA-BA43-809A477624E0}"/>
+    <hyperlink ref="J27" r:id="rId13" xr:uid="{7368B6D0-0B1E-4F4C-A87E-8F610FBEF48B}"/>
+    <hyperlink ref="J26" r:id="rId14" xr:uid="{08E7C8A9-7FA6-4545-955D-0FD9DC94652F}"/>
+    <hyperlink ref="J25" r:id="rId15" xr:uid="{F7D270FA-FA53-4557-9441-AD5535AB928F}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId16"/>
   </tableParts>
 </worksheet>
 </file>
--- a/trades.xlsx
+++ b/trades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\trading-journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{724141F5-5EF1-4A3D-B8DA-1E82EDCB0DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5458EDAE-C9E7-433C-B261-AF3DA36E9DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="86280" yWindow="-5520" windowWidth="16440" windowHeight="29040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="43">
   <si>
     <t>Trading Journal - Trade Log</t>
   </si>
@@ -144,6 +144,24 @@
   </si>
   <si>
     <t>https://thefreechart.com/x/UxZXxJr9/</t>
+  </si>
+  <si>
+    <t>https://thefreechart.com/x/Cwoh9hB4/</t>
+  </si>
+  <si>
+    <t>https://thefreechart.com/x/j7yR1HkK/</t>
+  </si>
+  <si>
+    <t>https://thefreechart.com/x/lVJ65f2J/</t>
+  </si>
+  <si>
+    <t>https://thefreechart.com/x/gEMtlS8B/</t>
+  </si>
+  <si>
+    <t>https://thefreechart.com/x/xeuJGC4m/</t>
+  </si>
+  <si>
+    <t>https://thefreechart.com/x/ZXVmx8QG/</t>
   </si>
 </sst>
 </file>
@@ -1516,232 +1534,498 @@
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="4"/>
-      <c r="B39" s="5"/>
+      <c r="A39" s="4">
+        <v>36</v>
+      </c>
+      <c r="B39" s="5">
+        <v>43838</v>
+      </c>
       <c r="C39" s="6"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
+      <c r="D39" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="7"/>
-      <c r="J39" s="7"/>
+      <c r="H39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="4"/>
-      <c r="B40" s="5"/>
+      <c r="A40" s="4">
+        <v>37</v>
+      </c>
+      <c r="B40" s="5">
+        <v>43847</v>
+      </c>
       <c r="C40" s="6"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
+      <c r="D40" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="7"/>
-      <c r="J40" s="7"/>
+      <c r="H40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="4"/>
-      <c r="B41" s="5"/>
+      <c r="A41" s="4">
+        <v>38</v>
+      </c>
+      <c r="B41" s="5">
+        <v>43852</v>
+      </c>
       <c r="C41" s="6"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
+      <c r="D41" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="7"/>
-      <c r="J41" s="7"/>
+      <c r="H41" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="4"/>
-      <c r="B42" s="5"/>
+      <c r="A42" s="4">
+        <v>39</v>
+      </c>
+      <c r="B42" s="5">
+        <v>43871</v>
+      </c>
       <c r="C42" s="6"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
+      <c r="D42" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="7"/>
-      <c r="J42" s="7"/>
+      <c r="H42" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J42" s="8" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" s="4"/>
-      <c r="B43" s="5"/>
+      <c r="A43" s="4">
+        <v>40</v>
+      </c>
+      <c r="B43" s="5">
+        <v>43873</v>
+      </c>
       <c r="C43" s="6"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
+      <c r="D43" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="7"/>
-      <c r="J43" s="7"/>
+      <c r="H43" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="4"/>
-      <c r="B44" s="5"/>
+      <c r="A44" s="4">
+        <v>41</v>
+      </c>
+      <c r="B44" s="5">
+        <v>43888</v>
+      </c>
       <c r="C44" s="6"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
+      <c r="D44" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="7"/>
-      <c r="J44" s="7"/>
+      <c r="H44" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="4"/>
-      <c r="B45" s="5"/>
+      <c r="A45" s="4">
+        <v>42</v>
+      </c>
+      <c r="B45" s="5">
+        <v>43893</v>
+      </c>
       <c r="C45" s="6"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
+      <c r="D45" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="7"/>
-      <c r="J45" s="7"/>
+      <c r="H45" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" s="4"/>
-      <c r="B46" s="5"/>
+      <c r="A46" s="4">
+        <v>43</v>
+      </c>
+      <c r="B46" s="5">
+        <v>43902</v>
+      </c>
       <c r="C46" s="6"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
+      <c r="D46" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="7"/>
+      <c r="H46" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I46" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J46" s="8" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="4"/>
-      <c r="B47" s="5"/>
+      <c r="A47" s="4">
+        <v>44</v>
+      </c>
+      <c r="B47" s="5">
+        <v>43910</v>
+      </c>
       <c r="C47" s="6"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
+      <c r="D47" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="7"/>
-      <c r="J47" s="7"/>
+      <c r="H47" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J47" s="8" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" s="4"/>
-      <c r="B48" s="5"/>
+      <c r="A48" s="4">
+        <v>45</v>
+      </c>
+      <c r="B48" s="5">
+        <v>43913</v>
+      </c>
       <c r="C48" s="6"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
+      <c r="D48" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="7"/>
-      <c r="J48" s="7"/>
+      <c r="H48" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I48" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J48" s="8" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" s="4"/>
-      <c r="B49" s="5"/>
+      <c r="A49" s="4">
+        <v>46</v>
+      </c>
+      <c r="B49" s="5">
+        <v>43919</v>
+      </c>
       <c r="C49" s="6"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
+      <c r="D49" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="7"/>
-      <c r="J49" s="7"/>
+      <c r="H49" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I49" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J49" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="4"/>
-      <c r="B50" s="5"/>
+      <c r="A50" s="4">
+        <v>47</v>
+      </c>
+      <c r="B50" s="5">
+        <v>43923</v>
+      </c>
       <c r="C50" s="6"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
+      <c r="D50" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="7"/>
+      <c r="H50" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I50" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J50" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="4"/>
-      <c r="B51" s="5"/>
+      <c r="A51" s="4">
+        <v>48</v>
+      </c>
+      <c r="B51" s="5">
+        <v>43929</v>
+      </c>
       <c r="C51" s="6"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
+      <c r="D51" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="7"/>
+      <c r="H51" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I51" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J51" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="4"/>
-      <c r="B52" s="5"/>
+      <c r="A52" s="4">
+        <v>49</v>
+      </c>
+      <c r="B52" s="5">
+        <v>43950</v>
+      </c>
       <c r="C52" s="6"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
+      <c r="D52" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="7"/>
+      <c r="H52" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I52" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J52" s="8" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" s="4"/>
-      <c r="B53" s="5"/>
+      <c r="A53" s="4">
+        <v>50</v>
+      </c>
+      <c r="B53" s="5">
+        <v>43957</v>
+      </c>
       <c r="C53" s="6"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
+      <c r="D53" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="7"/>
-      <c r="J53" s="7"/>
+      <c r="H53" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I53" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J53" s="8" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" s="4"/>
-      <c r="B54" s="5"/>
+      <c r="A54" s="4">
+        <v>51</v>
+      </c>
+      <c r="B54" s="5">
+        <v>43959</v>
+      </c>
       <c r="C54" s="6"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
+      <c r="D54" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
+      <c r="H54" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I54" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="4"/>
-      <c r="B55" s="5"/>
+      <c r="A55" s="4">
+        <v>52</v>
+      </c>
+      <c r="B55" s="5">
+        <v>43965</v>
+      </c>
       <c r="C55" s="6"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
+      <c r="D55" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="7"/>
+      <c r="H55" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I55" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J55" s="8" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56" s="4"/>
-      <c r="B56" s="5"/>
+      <c r="A56" s="4">
+        <v>53</v>
+      </c>
+      <c r="B56" s="5">
+        <v>43999</v>
+      </c>
       <c r="C56" s="6"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
+      <c r="D56" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="7"/>
-      <c r="J56" s="7"/>
+      <c r="H56" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I56" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" s="4"/>
-      <c r="B57" s="5"/>
+      <c r="A57" s="4">
+        <v>54</v>
+      </c>
+      <c r="B57" s="5">
+        <v>44012</v>
+      </c>
       <c r="C57" s="6"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
+      <c r="D57" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="7"/>
-      <c r="J57" s="7"/>
+      <c r="H57" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I57" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J57" s="8" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="4"/>
@@ -13078,10 +13362,29 @@
     <hyperlink ref="J27" r:id="rId13" xr:uid="{7368B6D0-0B1E-4F4C-A87E-8F610FBEF48B}"/>
     <hyperlink ref="J26" r:id="rId14" xr:uid="{08E7C8A9-7FA6-4545-955D-0FD9DC94652F}"/>
     <hyperlink ref="J25" r:id="rId15" xr:uid="{F7D270FA-FA53-4557-9441-AD5535AB928F}"/>
+    <hyperlink ref="J57" r:id="rId16" xr:uid="{3F80F065-C529-4E83-9D49-5E2A92D3E20F}"/>
+    <hyperlink ref="J56" r:id="rId17" xr:uid="{CB6A84F4-E526-44D0-BFD9-D4891321299F}"/>
+    <hyperlink ref="J55" r:id="rId18" xr:uid="{B5821B7E-FFEE-457F-BC3A-B1A8E1605E2D}"/>
+    <hyperlink ref="J54" r:id="rId19" xr:uid="{1586F033-F384-4A77-AF63-0C332656CAAF}"/>
+    <hyperlink ref="J53" r:id="rId20" xr:uid="{D3AA1163-946D-4C31-BD64-4462A5C9A245}"/>
+    <hyperlink ref="J52" r:id="rId21" xr:uid="{71841635-3EC3-4884-BDA2-EDA115C60017}"/>
+    <hyperlink ref="J51" r:id="rId22" xr:uid="{2EF60593-4A31-4838-9B5B-62F6BC07246C}"/>
+    <hyperlink ref="J50" r:id="rId23" xr:uid="{32CD4B33-8A0E-4091-B011-F395D602F72D}"/>
+    <hyperlink ref="J49" r:id="rId24" xr:uid="{E769E6A4-557D-4F95-80CA-C895D06B2097}"/>
+    <hyperlink ref="J48" r:id="rId25" xr:uid="{97646962-71D6-480F-ABD1-08C65F2C914A}"/>
+    <hyperlink ref="J47" r:id="rId26" xr:uid="{CC981D48-5124-4CFC-86C4-75570F84FAAC}"/>
+    <hyperlink ref="J46" r:id="rId27" xr:uid="{84F474BA-7FBB-4141-AC11-F099ABE9128A}"/>
+    <hyperlink ref="J45" r:id="rId28" xr:uid="{6EBD1B4D-1DAE-4665-8096-2229E4E7E6FA}"/>
+    <hyperlink ref="J44" r:id="rId29" xr:uid="{945608DB-F5F1-4F00-8BF1-D42277ADEF4A}"/>
+    <hyperlink ref="J43" r:id="rId30" xr:uid="{78B964B8-9DBC-415B-91CD-AFAE64A11563}"/>
+    <hyperlink ref="J42" r:id="rId31" xr:uid="{346DCFB0-9331-403F-A200-3018417457F9}"/>
+    <hyperlink ref="J41" r:id="rId32" xr:uid="{F35F0F38-4097-4409-AAD6-AB2E8412A02F}"/>
+    <hyperlink ref="J40" r:id="rId33" xr:uid="{CE580CE0-F5AD-4F88-8E28-6F85981B485A}"/>
+    <hyperlink ref="J39" r:id="rId34" xr:uid="{D3C26551-D22C-45DC-85CE-0850C0BC13F4}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart r:id="rId16"/>
+    <tablePart r:id="rId35"/>
   </tableParts>
 </worksheet>
 </file>
--- a/trades.xlsx
+++ b/trades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\trading-journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5458EDAE-C9E7-433C-B261-AF3DA36E9DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98ACC70A-14FE-49BD-B649-86E97A231758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="86280" yWindow="-5520" windowWidth="16440" windowHeight="29040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="34">
   <si>
     <t>Trading Journal - Trade Log</t>
   </si>
@@ -77,16 +77,7 @@
     <t>BUY</t>
   </si>
   <si>
-    <t>London</t>
-  </si>
-  <si>
-    <t>Breakout</t>
-  </si>
-  <si>
     <t>SL</t>
-  </si>
-  <si>
-    <t>Entered early</t>
   </si>
   <si>
     <t>GBPUSD</t>
@@ -95,37 +86,7 @@
     <t>SELL</t>
   </si>
   <si>
-    <t>New York</t>
-  </si>
-  <si>
-    <t>Supply zone</t>
-  </si>
-  <si>
-    <t>Liquidity sweep</t>
-  </si>
-  <si>
     <t>TP</t>
-  </si>
-  <si>
-    <t>Clean setup</t>
-  </si>
-  <si>
-    <t>Asia</t>
-  </si>
-  <si>
-    <t>Range</t>
-  </si>
-  <si>
-    <t>Pullback</t>
-  </si>
-  <si>
-    <t>BE</t>
-  </si>
-  <si>
-    <t>Moved SL to BEEE</t>
-  </si>
-  <si>
-    <t>https://www.tradingview.com/x/j2XJvs6h/</t>
   </si>
   <si>
     <t>Trendline</t>
@@ -162,6 +123,18 @@
   </si>
   <si>
     <t>https://thefreechart.com/x/ZXVmx8QG/</t>
+  </si>
+  <si>
+    <t>https://thefreechart.com/x/2B1HV155/</t>
+  </si>
+  <si>
+    <t>https://thefreechart.com/x/eQTyCii4/</t>
+  </si>
+  <si>
+    <t>https://thefreechart.com/x/c0QOJBaQ/</t>
+  </si>
+  <si>
+    <t>https://thefreechart.com/x/tmPHXDtT/</t>
   </si>
 </sst>
 </file>
@@ -278,8 +251,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TradeLog" displayName="TradeLog" ref="A3:J999">
-  <autoFilter ref="A3:J999" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TradeLog" displayName="TradeLog" ref="A3:J994">
+  <autoFilter ref="A3:J994" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Trade No"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Date"/>
@@ -581,10 +554,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J999"/>
+  <dimension ref="A1:J994"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="9" customWidth="1"/>
     <col min="4" max="5" width="12" customWidth="1"/>
@@ -642,57 +615,45 @@
         <v>1</v>
       </c>
       <c r="B4" s="5">
-        <v>46266</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0.34375</v>
-      </c>
+        <v>43839</v>
+      </c>
+      <c r="C4" s="6"/>
       <c r="D4" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>30</v>
-      </c>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>2</v>
       </c>
       <c r="B5" s="5">
-        <v>46267</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0.56944444444444442</v>
-      </c>
+        <v>43844</v>
+      </c>
+      <c r="C5" s="6"/>
       <c r="D5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="H5" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
@@ -702,29 +663,23 @@
         <v>3</v>
       </c>
       <c r="B6" s="5">
-        <v>46269</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0.37847222222222221</v>
-      </c>
+        <v>43854</v>
+      </c>
+      <c r="C6" s="6"/>
       <c r="D6" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>24</v>
-      </c>
+      <c r="I6" s="7"/>
       <c r="J6" s="7"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -732,25 +687,21 @@
         <v>4</v>
       </c>
       <c r="B7" s="5">
-        <v>46273</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.1041666666666667</v>
-      </c>
+        <v>43854</v>
+      </c>
+      <c r="C7" s="6"/>
       <c r="D7" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>25</v>
-      </c>
+      <c r="F7" s="4"/>
       <c r="G7" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -760,29 +711,23 @@
         <v>5</v>
       </c>
       <c r="B8" s="5">
-        <v>46275</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0.59027777777777779</v>
-      </c>
+        <v>43860</v>
+      </c>
+      <c r="C8" s="6"/>
       <c r="D8" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>29</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I8" s="7"/>
       <c r="J8" s="7"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -790,23 +735,23 @@
         <v>6</v>
       </c>
       <c r="B9" s="5">
-        <v>43839</v>
+        <v>43879</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I9" s="7"/>
       <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -814,23 +759,23 @@
         <v>7</v>
       </c>
       <c r="B10" s="5">
-        <v>43844</v>
+        <v>43900</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I10" s="7"/>
       <c r="J10" s="7"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -838,23 +783,23 @@
         <v>8</v>
       </c>
       <c r="B11" s="5">
-        <v>43854</v>
+        <v>43915</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -862,23 +807,23 @@
         <v>9</v>
       </c>
       <c r="B12" s="5">
-        <v>43854</v>
+        <v>43923</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
       <c r="H12" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I12" s="7"/>
       <c r="J12" s="7"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -886,23 +831,23 @@
         <v>10</v>
       </c>
       <c r="B13" s="5">
-        <v>43860</v>
+        <v>43935</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I13" s="7"/>
       <c r="J13" s="7"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -910,23 +855,23 @@
         <v>11</v>
       </c>
       <c r="B14" s="5">
-        <v>43879</v>
+        <v>43943</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
+      <c r="G14" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H14" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I14" s="7"/>
       <c r="J14" s="7"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -934,23 +879,23 @@
         <v>12</v>
       </c>
       <c r="B15" s="5">
-        <v>43900</v>
+        <v>43955</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
       <c r="H15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I15" s="7"/>
       <c r="J15" s="7"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -958,23 +903,23 @@
         <v>13</v>
       </c>
       <c r="B16" s="5">
-        <v>43915</v>
+        <v>43957</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
       <c r="H16" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I16" s="7"/>
       <c r="J16" s="7"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -982,23 +927,23 @@
         <v>14</v>
       </c>
       <c r="B17" s="5">
-        <v>43923</v>
+        <v>43957</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
       <c r="H17" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I17" s="7"/>
       <c r="J17" s="7"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
@@ -1006,23 +951,23 @@
         <v>15</v>
       </c>
       <c r="B18" s="5">
-        <v>43935</v>
+        <v>43972</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
       <c r="H18" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I18" s="7"/>
       <c r="J18" s="7"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
@@ -1030,23 +975,23 @@
         <v>16</v>
       </c>
       <c r="B19" s="5">
-        <v>43943</v>
+        <v>43980</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
+      <c r="G19" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H19" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I19" s="7"/>
       <c r="J19" s="7"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -1054,145 +999,155 @@
         <v>17</v>
       </c>
       <c r="B20" s="5">
-        <v>43955</v>
+        <v>44036</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
+      <c r="G20" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H20" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J20" s="7"/>
+        <v>17</v>
+      </c>
+      <c r="I20" s="7"/>
+      <c r="J20" s="8" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>18</v>
       </c>
       <c r="B21" s="5">
-        <v>43957</v>
+        <v>44053</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
       <c r="H21" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J21" s="7"/>
+        <v>14</v>
+      </c>
+      <c r="I21" s="7"/>
+      <c r="J21" s="8" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>19</v>
       </c>
       <c r="B22" s="5">
-        <v>43957</v>
+        <v>44061</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
       <c r="H22" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J22" s="7"/>
+        <v>14</v>
+      </c>
+      <c r="I22" s="7"/>
+      <c r="J22" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>20</v>
       </c>
       <c r="B23" s="5">
-        <v>43972</v>
+        <v>44076</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
       <c r="H23" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J23" s="7"/>
+        <v>14</v>
+      </c>
+      <c r="I23" s="7"/>
+      <c r="J23" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>21</v>
       </c>
       <c r="B24" s="5">
-        <v>43980</v>
+        <v>44082</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
       <c r="H24" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J24" s="7"/>
+        <v>17</v>
+      </c>
+      <c r="I24" s="7"/>
+      <c r="J24" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>22</v>
       </c>
       <c r="B25" s="5">
-        <v>44036</v>
+        <v>44109</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
+      <c r="G25" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H25" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I25" s="7"/>
       <c r="J25" s="8" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
@@ -1200,25 +1155,25 @@
         <v>23</v>
       </c>
       <c r="B26" s="5">
-        <v>44053</v>
+        <v>44138</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
+      <c r="G26" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H26" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I26" s="7"/>
       <c r="J26" s="8" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
@@ -1226,25 +1181,25 @@
         <v>24</v>
       </c>
       <c r="B27" s="5">
-        <v>44061</v>
+        <v>44140</v>
       </c>
       <c r="C27" s="6"/>
       <c r="D27" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
+      <c r="G27" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H27" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I27" s="7"/>
       <c r="J27" s="8" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
@@ -1252,25 +1207,25 @@
         <v>25</v>
       </c>
       <c r="B28" s="5">
-        <v>44076</v>
+        <v>44158</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
       <c r="H28" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I28" s="7"/>
       <c r="J28" s="8" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
@@ -1278,25 +1233,25 @@
         <v>26</v>
       </c>
       <c r="B29" s="5">
-        <v>44082</v>
+        <v>44167</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="H29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" s="7"/>
+      <c r="J29" s="8" t="s">
         <v>19</v>
-      </c>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J29" s="8" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
@@ -1304,25 +1259,25 @@
         <v>27</v>
       </c>
       <c r="B30" s="5">
-        <v>44109</v>
+        <v>44175</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
+      <c r="G30" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H30" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I30" s="7"/>
       <c r="J30" s="8" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
@@ -1330,25 +1285,25 @@
         <v>28</v>
       </c>
       <c r="B31" s="5">
-        <v>44138</v>
+        <v>44176</v>
       </c>
       <c r="C31" s="6"/>
       <c r="D31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E31" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
       <c r="H31" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I31" s="7"/>
       <c r="J31" s="8" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
@@ -1356,25 +1311,25 @@
         <v>29</v>
       </c>
       <c r="B32" s="5">
-        <v>44140</v>
+        <v>44188</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
+      <c r="G32" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H32" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I32" s="7"/>
       <c r="J32" s="8" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
@@ -1382,25 +1337,25 @@
         <v>30</v>
       </c>
       <c r="B33" s="5">
-        <v>44158</v>
+        <v>44193</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E33" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
       <c r="H33" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I33" s="7"/>
       <c r="J33" s="8" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
@@ -1408,25 +1363,25 @@
         <v>31</v>
       </c>
       <c r="B34" s="5">
-        <v>44167</v>
+        <v>43838</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E34" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
       <c r="H34" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I34" s="7"/>
       <c r="J34" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
@@ -1434,25 +1389,25 @@
         <v>32</v>
       </c>
       <c r="B35" s="5">
-        <v>44175</v>
+        <v>43847</v>
       </c>
       <c r="C35" s="6"/>
       <c r="D35" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
+      <c r="G35" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H35" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I35" s="7"/>
       <c r="J35" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
@@ -1460,25 +1415,25 @@
         <v>33</v>
       </c>
       <c r="B36" s="5">
-        <v>44176</v>
+        <v>43852</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E36" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
       <c r="H36" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I36" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I36" s="7"/>
       <c r="J36" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
@@ -1486,25 +1441,25 @@
         <v>34</v>
       </c>
       <c r="B37" s="5">
-        <v>44188</v>
+        <v>43871</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E37" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
       <c r="H37" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I37" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I37" s="7"/>
       <c r="J37" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
@@ -1512,25 +1467,25 @@
         <v>35</v>
       </c>
       <c r="B38" s="5">
-        <v>44193</v>
+        <v>43873</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E38" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
       <c r="H38" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I38" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I38" s="7"/>
       <c r="J38" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
@@ -1538,25 +1493,25 @@
         <v>36</v>
       </c>
       <c r="B39" s="5">
-        <v>43838</v>
+        <v>43888</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
+      <c r="G39" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H39" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I39" s="7"/>
       <c r="J39" s="8" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
@@ -1564,7 +1519,7 @@
         <v>37</v>
       </c>
       <c r="B40" s="5">
-        <v>43847</v>
+        <v>43893</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="4" t="s">
@@ -1574,15 +1529,15 @@
         <v>13</v>
       </c>
       <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
+      <c r="G40" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H40" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I40" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I40" s="7"/>
       <c r="J40" s="8" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
@@ -1590,25 +1545,25 @@
         <v>38</v>
       </c>
       <c r="B41" s="5">
-        <v>43852</v>
+        <v>43902</v>
       </c>
       <c r="C41" s="6"/>
       <c r="D41" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
+      <c r="G41" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H41" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I41" s="7"/>
       <c r="J41" s="8" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
@@ -1616,25 +1571,25 @@
         <v>39</v>
       </c>
       <c r="B42" s="5">
-        <v>43871</v>
+        <v>43910</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
+      <c r="G42" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H42" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I42" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I42" s="7"/>
       <c r="J42" s="8" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
@@ -1642,7 +1597,7 @@
         <v>40</v>
       </c>
       <c r="B43" s="5">
-        <v>43873</v>
+        <v>43913</v>
       </c>
       <c r="C43" s="6"/>
       <c r="D43" s="4" t="s">
@@ -1652,15 +1607,15 @@
         <v>13</v>
       </c>
       <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
+      <c r="G43" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H43" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I43" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I43" s="7"/>
       <c r="J43" s="8" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
@@ -1668,25 +1623,25 @@
         <v>41</v>
       </c>
       <c r="B44" s="5">
-        <v>43888</v>
+        <v>43919</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
+      <c r="G44" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H44" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I44" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I44" s="7"/>
       <c r="J44" s="8" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
@@ -1694,7 +1649,7 @@
         <v>42</v>
       </c>
       <c r="B45" s="5">
-        <v>43893</v>
+        <v>43923</v>
       </c>
       <c r="C45" s="6"/>
       <c r="D45" s="4" t="s">
@@ -1704,15 +1659,15 @@
         <v>13</v>
       </c>
       <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
+      <c r="G45" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H45" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I45" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I45" s="7"/>
       <c r="J45" s="8" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
@@ -1720,25 +1675,25 @@
         <v>43</v>
       </c>
       <c r="B46" s="5">
-        <v>43902</v>
+        <v>43929</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
+      <c r="G46" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H46" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I46" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I46" s="7"/>
       <c r="J46" s="8" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
@@ -1746,7 +1701,7 @@
         <v>44</v>
       </c>
       <c r="B47" s="5">
-        <v>43910</v>
+        <v>43950</v>
       </c>
       <c r="C47" s="6"/>
       <c r="D47" s="4" t="s">
@@ -1756,15 +1711,15 @@
         <v>13</v>
       </c>
       <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
+      <c r="G47" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H47" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I47" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I47" s="7"/>
       <c r="J47" s="8" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
@@ -1772,25 +1727,25 @@
         <v>45</v>
       </c>
       <c r="B48" s="5">
-        <v>43913</v>
+        <v>43957</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
+      <c r="G48" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H48" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I48" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I48" s="7"/>
       <c r="J48" s="8" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
@@ -1798,25 +1753,25 @@
         <v>46</v>
       </c>
       <c r="B49" s="5">
-        <v>43919</v>
+        <v>43959</v>
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
+      <c r="G49" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H49" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I49" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I49" s="7"/>
       <c r="J49" s="8" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
@@ -1824,7 +1779,7 @@
         <v>47</v>
       </c>
       <c r="B50" s="5">
-        <v>43923</v>
+        <v>43965</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="4" t="s">
@@ -1834,15 +1789,15 @@
         <v>13</v>
       </c>
       <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
+      <c r="G50" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H50" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I50" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I50" s="7"/>
       <c r="J50" s="8" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
@@ -1850,7 +1805,7 @@
         <v>48</v>
       </c>
       <c r="B51" s="5">
-        <v>43929</v>
+        <v>43999</v>
       </c>
       <c r="C51" s="6"/>
       <c r="D51" s="4" t="s">
@@ -1860,15 +1815,15 @@
         <v>13</v>
       </c>
       <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
+      <c r="G51" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H51" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I51" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I51" s="7"/>
       <c r="J51" s="8" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
@@ -1876,7 +1831,7 @@
         <v>49</v>
       </c>
       <c r="B52" s="5">
-        <v>43950</v>
+        <v>44012</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="4" t="s">
@@ -1886,15 +1841,15 @@
         <v>13</v>
       </c>
       <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
+      <c r="G52" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H52" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I52" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I52" s="7"/>
       <c r="J52" s="8" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
@@ -1902,25 +1857,25 @@
         <v>50</v>
       </c>
       <c r="B53" s="5">
-        <v>43957</v>
+        <v>44025</v>
       </c>
       <c r="C53" s="6"/>
       <c r="D53" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
+      <c r="G53" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H53" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I53" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I53" s="7"/>
       <c r="J53" s="8" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
@@ -1928,25 +1883,25 @@
         <v>51</v>
       </c>
       <c r="B54" s="5">
-        <v>43959</v>
+        <v>44026</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
+      <c r="G54" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H54" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I54" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I54" s="7"/>
       <c r="J54" s="8" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
@@ -1954,25 +1909,25 @@
         <v>52</v>
       </c>
       <c r="B55" s="5">
-        <v>43965</v>
+        <v>44040</v>
       </c>
       <c r="C55" s="6"/>
       <c r="D55" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
+      <c r="G55" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H55" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I55" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I55" s="7"/>
       <c r="J55" s="8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
@@ -1980,25 +1935,25 @@
         <v>53</v>
       </c>
       <c r="B56" s="5">
-        <v>43999</v>
+        <v>44061</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
+      <c r="G56" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H56" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I56" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I56" s="7"/>
       <c r="J56" s="8" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
@@ -2006,7 +1961,7 @@
         <v>54</v>
       </c>
       <c r="B57" s="5">
-        <v>44012</v>
+        <v>44102</v>
       </c>
       <c r="C57" s="6"/>
       <c r="D57" s="4" t="s">
@@ -2016,88 +1971,172 @@
         <v>13</v>
       </c>
       <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
+      <c r="G57" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H57" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I57" s="7"/>
+      <c r="J57" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" s="4">
+        <v>55</v>
+      </c>
+      <c r="B58" s="5">
+        <v>44112</v>
+      </c>
+      <c r="C58" s="6"/>
+      <c r="D58" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I58" s="7"/>
+      <c r="J58" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" s="4">
+        <v>56</v>
+      </c>
+      <c r="B59" s="5">
+        <v>44117</v>
+      </c>
+      <c r="C59" s="6"/>
+      <c r="D59" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E59" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I57" s="7" t="s">
+      <c r="F59" s="4"/>
+      <c r="G59" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I59" s="7"/>
+      <c r="J59" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="J57" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" s="4"/>
-      <c r="B58" s="5"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="7"/>
-      <c r="J58" s="7"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59" s="4"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
-      <c r="I59" s="7"/>
-      <c r="J59" s="7"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A60" s="4"/>
-      <c r="B60" s="5"/>
+      <c r="A60" s="4">
+        <v>57</v>
+      </c>
+      <c r="B60" s="5">
+        <v>44124</v>
+      </c>
       <c r="C60" s="6"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
+      <c r="D60" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
+      <c r="G60" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="I60" s="7"/>
-      <c r="J60" s="7"/>
+      <c r="J60" s="8" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A61" s="4"/>
-      <c r="B61" s="5"/>
+      <c r="A61" s="4">
+        <v>58</v>
+      </c>
+      <c r="B61" s="5">
+        <v>44155</v>
+      </c>
       <c r="C61" s="6"/>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
+      <c r="D61" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
+      <c r="G61" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="I61" s="7"/>
-      <c r="J61" s="7"/>
+      <c r="J61" s="8" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A62" s="4"/>
-      <c r="B62" s="5"/>
+      <c r="A62" s="4">
+        <v>59</v>
+      </c>
+      <c r="B62" s="5">
+        <v>44158</v>
+      </c>
       <c r="C62" s="6"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
+      <c r="D62" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
+      <c r="G62" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="I62" s="7"/>
-      <c r="J62" s="7"/>
+      <c r="J62" s="8" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A63" s="4"/>
-      <c r="B63" s="5"/>
+      <c r="A63" s="4">
+        <v>60</v>
+      </c>
+      <c r="B63" s="5">
+        <v>44162</v>
+      </c>
       <c r="C63" s="6"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
+      <c r="D63" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F63" s="4"/>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4"/>
+      <c r="G63" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="I63" s="7"/>
-      <c r="J63" s="7"/>
+      <c r="J63" s="8" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="4"/>
@@ -13271,120 +13310,70 @@
       <c r="I994" s="7"/>
       <c r="J994" s="7"/>
     </row>
-    <row r="995" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A995" s="4"/>
-      <c r="B995" s="5"/>
-      <c r="C995" s="6"/>
-      <c r="D995" s="4"/>
-      <c r="E995" s="4"/>
-      <c r="F995" s="4"/>
-      <c r="G995" s="4"/>
-      <c r="H995" s="4"/>
-      <c r="I995" s="7"/>
-      <c r="J995" s="7"/>
-    </row>
-    <row r="996" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A996" s="4"/>
-      <c r="B996" s="5"/>
-      <c r="C996" s="6"/>
-      <c r="D996" s="4"/>
-      <c r="E996" s="4"/>
-      <c r="F996" s="4"/>
-      <c r="G996" s="4"/>
-      <c r="H996" s="4"/>
-      <c r="I996" s="7"/>
-      <c r="J996" s="7"/>
-    </row>
-    <row r="997" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A997" s="4"/>
-      <c r="B997" s="5"/>
-      <c r="C997" s="6"/>
-      <c r="D997" s="4"/>
-      <c r="E997" s="4"/>
-      <c r="F997" s="4"/>
-      <c r="G997" s="4"/>
-      <c r="H997" s="4"/>
-      <c r="I997" s="7"/>
-      <c r="J997" s="7"/>
-    </row>
-    <row r="998" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A998" s="4"/>
-      <c r="B998" s="5"/>
-      <c r="C998" s="6"/>
-      <c r="D998" s="4"/>
-      <c r="E998" s="4"/>
-      <c r="F998" s="4"/>
-      <c r="G998" s="4"/>
-      <c r="H998" s="4"/>
-      <c r="I998" s="7"/>
-      <c r="J998" s="7"/>
-    </row>
-    <row r="999" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A999" s="4"/>
-      <c r="B999" s="5"/>
-      <c r="C999" s="6"/>
-      <c r="D999" s="4"/>
-      <c r="E999" s="4"/>
-      <c r="F999" s="4"/>
-      <c r="G999" s="4"/>
-      <c r="H999" s="4"/>
-      <c r="I999" s="7"/>
-      <c r="J999" s="7"/>
-    </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="Pick a market (edit this list under Data &gt; Data Validation to add more)." sqref="D4:D999" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="Pick a market (edit this list under Data &gt; Data Validation to add more)." sqref="D4:D994" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"XAUUSD,ETHUSD,GBPUSD"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="BUY or SELL." sqref="E4:E999" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="BUY or SELL." sqref="E4:E994" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"BUY,SELL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="Pick a session." sqref="F4:F999" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="Pick a session." sqref="F4:F994" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Asia,London,New York"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="TP, SL or BE." sqref="H4:H999" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="TP, SL or BE." sqref="H4:H994" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"TP,SL,BE"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="J4" r:id="rId1" xr:uid="{886DD11E-A6A7-4084-8D9A-25624006ECAD}"/>
-    <hyperlink ref="J38" r:id="rId2" xr:uid="{623704F0-0601-4D2E-A751-8060B75B0D88}"/>
-    <hyperlink ref="J37" r:id="rId3" xr:uid="{91095999-FCFE-46CD-B204-6103E44B467A}"/>
-    <hyperlink ref="J36" r:id="rId4" xr:uid="{972561D1-305A-4282-A7B4-FCEDA6CFBF4F}"/>
-    <hyperlink ref="J35" r:id="rId5" xr:uid="{89A5A8BD-98C5-41AF-829C-BB1D611A1AFF}"/>
-    <hyperlink ref="J34" r:id="rId6" xr:uid="{4099F7B4-F6F2-4CB9-B096-97CB8EFC661F}"/>
-    <hyperlink ref="J33" r:id="rId7" xr:uid="{7027DC13-E5A1-49BC-9EDB-3D001113E112}"/>
-    <hyperlink ref="J32" r:id="rId8" xr:uid="{F4BCD004-CDAF-4893-8E1B-4834F72BDEC6}"/>
-    <hyperlink ref="J31" r:id="rId9" xr:uid="{D10218F1-074C-41F2-874F-0D6B2E299E04}"/>
-    <hyperlink ref="J30" r:id="rId10" xr:uid="{E5D9EFF4-0438-47AC-9448-8896FE8352C0}"/>
-    <hyperlink ref="J29" r:id="rId11" xr:uid="{78E4062F-AB6A-4DBD-BEC8-6C5101CCCBCF}"/>
-    <hyperlink ref="J28" r:id="rId12" xr:uid="{A2B82276-3248-4BBA-BA43-809A477624E0}"/>
-    <hyperlink ref="J27" r:id="rId13" xr:uid="{7368B6D0-0B1E-4F4C-A87E-8F610FBEF48B}"/>
-    <hyperlink ref="J26" r:id="rId14" xr:uid="{08E7C8A9-7FA6-4545-955D-0FD9DC94652F}"/>
-    <hyperlink ref="J25" r:id="rId15" xr:uid="{F7D270FA-FA53-4557-9441-AD5535AB928F}"/>
-    <hyperlink ref="J57" r:id="rId16" xr:uid="{3F80F065-C529-4E83-9D49-5E2A92D3E20F}"/>
-    <hyperlink ref="J56" r:id="rId17" xr:uid="{CB6A84F4-E526-44D0-BFD9-D4891321299F}"/>
-    <hyperlink ref="J55" r:id="rId18" xr:uid="{B5821B7E-FFEE-457F-BC3A-B1A8E1605E2D}"/>
-    <hyperlink ref="J54" r:id="rId19" xr:uid="{1586F033-F384-4A77-AF63-0C332656CAAF}"/>
-    <hyperlink ref="J53" r:id="rId20" xr:uid="{D3AA1163-946D-4C31-BD64-4462A5C9A245}"/>
-    <hyperlink ref="J52" r:id="rId21" xr:uid="{71841635-3EC3-4884-BDA2-EDA115C60017}"/>
-    <hyperlink ref="J51" r:id="rId22" xr:uid="{2EF60593-4A31-4838-9B5B-62F6BC07246C}"/>
-    <hyperlink ref="J50" r:id="rId23" xr:uid="{32CD4B33-8A0E-4091-B011-F395D602F72D}"/>
-    <hyperlink ref="J49" r:id="rId24" xr:uid="{E769E6A4-557D-4F95-80CA-C895D06B2097}"/>
-    <hyperlink ref="J48" r:id="rId25" xr:uid="{97646962-71D6-480F-ABD1-08C65F2C914A}"/>
-    <hyperlink ref="J47" r:id="rId26" xr:uid="{CC981D48-5124-4CFC-86C4-75570F84FAAC}"/>
-    <hyperlink ref="J46" r:id="rId27" xr:uid="{84F474BA-7FBB-4141-AC11-F099ABE9128A}"/>
-    <hyperlink ref="J45" r:id="rId28" xr:uid="{6EBD1B4D-1DAE-4665-8096-2229E4E7E6FA}"/>
-    <hyperlink ref="J44" r:id="rId29" xr:uid="{945608DB-F5F1-4F00-8BF1-D42277ADEF4A}"/>
-    <hyperlink ref="J43" r:id="rId30" xr:uid="{78B964B8-9DBC-415B-91CD-AFAE64A11563}"/>
-    <hyperlink ref="J42" r:id="rId31" xr:uid="{346DCFB0-9331-403F-A200-3018417457F9}"/>
-    <hyperlink ref="J41" r:id="rId32" xr:uid="{F35F0F38-4097-4409-AAD6-AB2E8412A02F}"/>
-    <hyperlink ref="J40" r:id="rId33" xr:uid="{CE580CE0-F5AD-4F88-8E28-6F85981B485A}"/>
-    <hyperlink ref="J39" r:id="rId34" xr:uid="{D3C26551-D22C-45DC-85CE-0850C0BC13F4}"/>
+    <hyperlink ref="J33" r:id="rId1" xr:uid="{623704F0-0601-4D2E-A751-8060B75B0D88}"/>
+    <hyperlink ref="J32" r:id="rId2" xr:uid="{91095999-FCFE-46CD-B204-6103E44B467A}"/>
+    <hyperlink ref="J31" r:id="rId3" xr:uid="{972561D1-305A-4282-A7B4-FCEDA6CFBF4F}"/>
+    <hyperlink ref="J30" r:id="rId4" xr:uid="{89A5A8BD-98C5-41AF-829C-BB1D611A1AFF}"/>
+    <hyperlink ref="J29" r:id="rId5" xr:uid="{4099F7B4-F6F2-4CB9-B096-97CB8EFC661F}"/>
+    <hyperlink ref="J28" r:id="rId6" xr:uid="{7027DC13-E5A1-49BC-9EDB-3D001113E112}"/>
+    <hyperlink ref="J27" r:id="rId7" xr:uid="{F4BCD004-CDAF-4893-8E1B-4834F72BDEC6}"/>
+    <hyperlink ref="J26" r:id="rId8" xr:uid="{D10218F1-074C-41F2-874F-0D6B2E299E04}"/>
+    <hyperlink ref="J25" r:id="rId9" xr:uid="{E5D9EFF4-0438-47AC-9448-8896FE8352C0}"/>
+    <hyperlink ref="J24" r:id="rId10" xr:uid="{78E4062F-AB6A-4DBD-BEC8-6C5101CCCBCF}"/>
+    <hyperlink ref="J23" r:id="rId11" xr:uid="{A2B82276-3248-4BBA-BA43-809A477624E0}"/>
+    <hyperlink ref="J22" r:id="rId12" xr:uid="{7368B6D0-0B1E-4F4C-A87E-8F610FBEF48B}"/>
+    <hyperlink ref="J21" r:id="rId13" xr:uid="{08E7C8A9-7FA6-4545-955D-0FD9DC94652F}"/>
+    <hyperlink ref="J20" r:id="rId14" xr:uid="{F7D270FA-FA53-4557-9441-AD5535AB928F}"/>
+    <hyperlink ref="J52" r:id="rId15" xr:uid="{3F80F065-C529-4E83-9D49-5E2A92D3E20F}"/>
+    <hyperlink ref="J51" r:id="rId16" xr:uid="{CB6A84F4-E526-44D0-BFD9-D4891321299F}"/>
+    <hyperlink ref="J50" r:id="rId17" xr:uid="{B5821B7E-FFEE-457F-BC3A-B1A8E1605E2D}"/>
+    <hyperlink ref="J49" r:id="rId18" xr:uid="{1586F033-F384-4A77-AF63-0C332656CAAF}"/>
+    <hyperlink ref="J48" r:id="rId19" xr:uid="{D3AA1163-946D-4C31-BD64-4462A5C9A245}"/>
+    <hyperlink ref="J47" r:id="rId20" xr:uid="{71841635-3EC3-4884-BDA2-EDA115C60017}"/>
+    <hyperlink ref="J46" r:id="rId21" xr:uid="{2EF60593-4A31-4838-9B5B-62F6BC07246C}"/>
+    <hyperlink ref="J45" r:id="rId22" xr:uid="{32CD4B33-8A0E-4091-B011-F395D602F72D}"/>
+    <hyperlink ref="J44" r:id="rId23" xr:uid="{E769E6A4-557D-4F95-80CA-C895D06B2097}"/>
+    <hyperlink ref="J43" r:id="rId24" xr:uid="{97646962-71D6-480F-ABD1-08C65F2C914A}"/>
+    <hyperlink ref="J42" r:id="rId25" xr:uid="{CC981D48-5124-4CFC-86C4-75570F84FAAC}"/>
+    <hyperlink ref="J41" r:id="rId26" xr:uid="{84F474BA-7FBB-4141-AC11-F099ABE9128A}"/>
+    <hyperlink ref="J40" r:id="rId27" xr:uid="{6EBD1B4D-1DAE-4665-8096-2229E4E7E6FA}"/>
+    <hyperlink ref="J39" r:id="rId28" xr:uid="{945608DB-F5F1-4F00-8BF1-D42277ADEF4A}"/>
+    <hyperlink ref="J38" r:id="rId29" xr:uid="{78B964B8-9DBC-415B-91CD-AFAE64A11563}"/>
+    <hyperlink ref="J37" r:id="rId30" xr:uid="{346DCFB0-9331-403F-A200-3018417457F9}"/>
+    <hyperlink ref="J36" r:id="rId31" xr:uid="{F35F0F38-4097-4409-AAD6-AB2E8412A02F}"/>
+    <hyperlink ref="J35" r:id="rId32" xr:uid="{CE580CE0-F5AD-4F88-8E28-6F85981B485A}"/>
+    <hyperlink ref="J34" r:id="rId33" xr:uid="{D3C26551-D22C-45DC-85CE-0850C0BC13F4}"/>
+    <hyperlink ref="J63" r:id="rId34" xr:uid="{585BC76A-2C2F-4ADF-9A68-ECCD0BD02B37}"/>
+    <hyperlink ref="J62" r:id="rId35" xr:uid="{693D7045-2BA3-4059-A1E6-F07F43739AF3}"/>
+    <hyperlink ref="J61" r:id="rId36" xr:uid="{850D8C42-9D23-46D7-B078-D8EB8E330CE4}"/>
+    <hyperlink ref="J60" r:id="rId37" xr:uid="{375A7453-E486-4207-B900-0AA42273A37B}"/>
+    <hyperlink ref="J59" r:id="rId38" xr:uid="{192BC11B-46AB-496C-8FE6-337B4014FCE1}"/>
+    <hyperlink ref="J58" r:id="rId39" xr:uid="{C92B0DD4-1551-4D1F-B83B-D01C1A5FE20A}"/>
+    <hyperlink ref="J57" r:id="rId40" xr:uid="{42D4F147-3337-499E-B706-361D0FB4D082}"/>
+    <hyperlink ref="J56" r:id="rId41" xr:uid="{5D5CE843-3120-42BD-A0C5-D7D7D5468082}"/>
+    <hyperlink ref="J55" r:id="rId42" xr:uid="{A279FAA2-98D8-438D-AE9A-EE0688D6A2AA}"/>
+    <hyperlink ref="J54" r:id="rId43" xr:uid="{91ABD0F5-EC16-4720-ADA2-328255DAE095}"/>
+    <hyperlink ref="J53" r:id="rId44" xr:uid="{4A1C2752-81C2-4BC2-9F4F-C2573E2624CF}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart r:id="rId35"/>
+    <tablePart r:id="rId45"/>
   </tableParts>
 </worksheet>
 </file>
--- a/trades.xlsx
+++ b/trades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\trading-journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98ACC70A-14FE-49BD-B649-86E97A231758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB46598-E4C1-413E-9475-B8BD332A2882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="86280" yWindow="-5520" windowWidth="16440" windowHeight="29040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="35">
   <si>
     <t>Trading Journal - Trade Log</t>
   </si>
@@ -135,6 +135,9 @@
   </si>
   <si>
     <t>https://thefreechart.com/x/tmPHXDtT/</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -2133,7 +2136,9 @@
       <c r="H63" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="I63" s="7"/>
+      <c r="I63" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="J63" s="8" t="s">
         <v>30</v>
       </c>

--- a/trades.xlsx
+++ b/trades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\trading-journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB46598-E4C1-413E-9475-B8BD332A2882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED4FB46-2B89-4686-BECE-1645DFB77F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="86280" yWindow="-5520" windowWidth="16440" windowHeight="29040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/trades.xlsx
+++ b/trades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\trading-journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED4FB46-2B89-4686-BECE-1645DFB77F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{306474F4-94D1-4F43-9AAD-F5F2CEE9BBDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="86280" yWindow="-5520" windowWidth="16440" windowHeight="29040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="43">
   <si>
     <t>Trading Journal - Trade Log</t>
   </si>
@@ -137,7 +137,31 @@
     <t>https://thefreechart.com/x/tmPHXDtT/</t>
   </si>
   <si>
-    <t>-</t>
+    <t>https://thefreechart.com/x/RUyir6o5/</t>
+  </si>
+  <si>
+    <t>https://thefreechart.com/x/ro5q4bK0/</t>
+  </si>
+  <si>
+    <t>https://thefreechart.com/x/i1Ent3yM/</t>
+  </si>
+  <si>
+    <t>https://thefreechart.com/x/jYmMKEES/</t>
+  </si>
+  <si>
+    <t>https://thefreechart.com/x/TCAlsMHO/</t>
+  </si>
+  <si>
+    <t>https://thefreechart.com/x/z6CZzxXc/</t>
+  </si>
+  <si>
+    <t>https://thefreechart.com/x/YX0k5EdM/</t>
+  </si>
+  <si>
+    <t>https://thefreechart.com/x/qO7A2fVp/</t>
+  </si>
+  <si>
+    <t>https://thefreechart.com/x/XOuJKDYy/</t>
   </si>
 </sst>
 </file>
@@ -2136,348 +2160,738 @@
       <c r="H63" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="I63" s="7" t="s">
-        <v>34</v>
-      </c>
+      <c r="I63" s="7"/>
       <c r="J63" s="8" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A64" s="4"/>
-      <c r="B64" s="5"/>
+      <c r="A64" s="4">
+        <v>61</v>
+      </c>
+      <c r="B64" s="5">
+        <v>44202</v>
+      </c>
       <c r="C64" s="6"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
+      <c r="D64" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
-      <c r="H64" s="4"/>
+      <c r="G64" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="I64" s="7"/>
-      <c r="J64" s="7"/>
+      <c r="J64" s="8" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A65" s="4"/>
-      <c r="B65" s="5"/>
+      <c r="A65" s="4">
+        <v>62</v>
+      </c>
+      <c r="B65" s="5">
+        <v>44216</v>
+      </c>
       <c r="C65" s="6"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
+      <c r="D65" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F65" s="4"/>
-      <c r="G65" s="4"/>
-      <c r="H65" s="4"/>
+      <c r="G65" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="I65" s="7"/>
-      <c r="J65" s="7"/>
+      <c r="J65" s="8" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A66" s="4"/>
-      <c r="B66" s="5"/>
+      <c r="A66" s="4">
+        <v>63</v>
+      </c>
+      <c r="B66" s="5">
+        <v>44231</v>
+      </c>
       <c r="C66" s="6"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
+      <c r="D66" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
-      <c r="H66" s="4"/>
+      <c r="G66" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="I66" s="7"/>
-      <c r="J66" s="7"/>
+      <c r="J66" s="8" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A67" s="4"/>
-      <c r="B67" s="5"/>
+      <c r="A67" s="4">
+        <v>64</v>
+      </c>
+      <c r="B67" s="5">
+        <v>44243</v>
+      </c>
       <c r="C67" s="6"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
+      <c r="D67" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F67" s="4"/>
-      <c r="G67" s="4"/>
-      <c r="H67" s="4"/>
+      <c r="G67" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="I67" s="7"/>
-      <c r="J67" s="7"/>
+      <c r="J67" s="8" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A68" s="4"/>
-      <c r="B68" s="5"/>
+      <c r="A68" s="4">
+        <v>65</v>
+      </c>
+      <c r="B68" s="5">
+        <v>44243</v>
+      </c>
       <c r="C68" s="6"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
+      <c r="D68" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
-      <c r="H68" s="4"/>
+      <c r="G68" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="I68" s="7"/>
-      <c r="J68" s="7"/>
+      <c r="J68" s="8" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A69" s="4"/>
-      <c r="B69" s="5"/>
+      <c r="A69" s="4">
+        <v>66</v>
+      </c>
+      <c r="B69" s="5">
+        <v>44246</v>
+      </c>
       <c r="C69" s="6"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
+      <c r="D69" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
+      <c r="G69" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="I69" s="7"/>
-      <c r="J69" s="7"/>
+      <c r="J69" s="8" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A70" s="4"/>
-      <c r="B70" s="5"/>
+      <c r="A70" s="4">
+        <v>67</v>
+      </c>
+      <c r="B70" s="5">
+        <v>44272</v>
+      </c>
       <c r="C70" s="6"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
+      <c r="D70" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F70" s="4"/>
-      <c r="G70" s="4"/>
-      <c r="H70" s="4"/>
+      <c r="G70" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="I70" s="7"/>
-      <c r="J70" s="7"/>
+      <c r="J70" s="8" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A71" s="4"/>
-      <c r="B71" s="5"/>
+      <c r="A71" s="4">
+        <v>68</v>
+      </c>
+      <c r="B71" s="5">
+        <v>44291</v>
+      </c>
       <c r="C71" s="6"/>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
+      <c r="D71" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F71" s="4"/>
-      <c r="G71" s="4"/>
-      <c r="H71" s="4"/>
+      <c r="G71" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="I71" s="7"/>
-      <c r="J71" s="7"/>
+      <c r="J71" s="8" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A72" s="4"/>
-      <c r="B72" s="5"/>
+      <c r="A72" s="4">
+        <v>69</v>
+      </c>
+      <c r="B72" s="5">
+        <v>44301</v>
+      </c>
       <c r="C72" s="6"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
+      <c r="D72" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4"/>
+      <c r="G72" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="I72" s="7"/>
-      <c r="J72" s="7"/>
+      <c r="J72" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A73" s="4"/>
-      <c r="B73" s="5"/>
+      <c r="A73" s="4">
+        <v>70</v>
+      </c>
+      <c r="B73" s="5">
+        <v>44313</v>
+      </c>
       <c r="C73" s="6"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
+      <c r="D73" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F73" s="4"/>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4"/>
+      <c r="G73" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="I73" s="7"/>
-      <c r="J73" s="7"/>
+      <c r="J73" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A74" s="4"/>
-      <c r="B74" s="5"/>
+      <c r="A74" s="4">
+        <v>71</v>
+      </c>
+      <c r="B74" s="5">
+        <v>44319</v>
+      </c>
       <c r="C74" s="6"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
+      <c r="D74" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
+      <c r="G74" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="I74" s="7"/>
-      <c r="J74" s="7"/>
+      <c r="J74" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A75" s="4"/>
-      <c r="B75" s="5"/>
+      <c r="A75" s="4">
+        <v>72</v>
+      </c>
+      <c r="B75" s="5">
+        <v>44333</v>
+      </c>
       <c r="C75" s="6"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
+      <c r="D75" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F75" s="4"/>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
+      <c r="G75" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="I75" s="7"/>
-      <c r="J75" s="7"/>
+      <c r="J75" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A76" s="4"/>
-      <c r="B76" s="5"/>
+      <c r="A76" s="4">
+        <v>73</v>
+      </c>
+      <c r="B76" s="5">
+        <v>44344</v>
+      </c>
       <c r="C76" s="6"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
+      <c r="D76" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F76" s="4"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="4"/>
+      <c r="G76" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="I76" s="7"/>
-      <c r="J76" s="7"/>
+      <c r="J76" s="8" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A77" s="4"/>
-      <c r="B77" s="5"/>
+      <c r="A77" s="4">
+        <v>74</v>
+      </c>
+      <c r="B77" s="5">
+        <v>44349</v>
+      </c>
       <c r="C77" s="6"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
+      <c r="D77" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
+      <c r="G77" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="I77" s="7"/>
-      <c r="J77" s="7"/>
+      <c r="J77" s="8" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A78" s="4"/>
-      <c r="B78" s="5"/>
+      <c r="A78" s="4">
+        <v>75</v>
+      </c>
+      <c r="B78" s="5">
+        <v>44370</v>
+      </c>
       <c r="C78" s="6"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
+      <c r="D78" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
+      <c r="G78" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="I78" s="7"/>
-      <c r="J78" s="7"/>
+      <c r="J78" s="8" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A79" s="4"/>
-      <c r="B79" s="5"/>
+      <c r="A79" s="4">
+        <v>76</v>
+      </c>
+      <c r="B79" s="5">
+        <v>44376</v>
+      </c>
       <c r="C79" s="6"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
+      <c r="D79" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
+      <c r="G79" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="I79" s="7"/>
-      <c r="J79" s="7"/>
+      <c r="J79" s="8" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A80" s="4"/>
-      <c r="B80" s="5"/>
+      <c r="A80" s="4">
+        <v>77</v>
+      </c>
+      <c r="B80" s="5">
+        <v>44368</v>
+      </c>
       <c r="C80" s="6"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
+      <c r="D80" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
+      <c r="G80" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="I80" s="7"/>
-      <c r="J80" s="7"/>
+      <c r="J80" s="8" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A81" s="4"/>
-      <c r="B81" s="5"/>
+      <c r="A81" s="4">
+        <v>78</v>
+      </c>
+      <c r="B81" s="5">
+        <v>44410</v>
+      </c>
       <c r="C81" s="6"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
+      <c r="D81" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F81" s="4"/>
-      <c r="G81" s="4"/>
-      <c r="H81" s="4"/>
+      <c r="G81" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="I81" s="7"/>
-      <c r="J81" s="7"/>
+      <c r="J81" s="8" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A82" s="4"/>
-      <c r="B82" s="5"/>
+      <c r="A82" s="4">
+        <v>79</v>
+      </c>
+      <c r="B82" s="5">
+        <v>44413</v>
+      </c>
       <c r="C82" s="6"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
+      <c r="D82" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F82" s="4"/>
-      <c r="G82" s="4"/>
-      <c r="H82" s="4"/>
+      <c r="G82" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="I82" s="7"/>
-      <c r="J82" s="7"/>
+      <c r="J82" s="8" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A83" s="4"/>
-      <c r="B83" s="5"/>
+      <c r="A83" s="4">
+        <v>80</v>
+      </c>
+      <c r="B83" s="5">
+        <v>44454</v>
+      </c>
       <c r="C83" s="6"/>
-      <c r="D83" s="4"/>
-      <c r="E83" s="4"/>
+      <c r="D83" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F83" s="4"/>
-      <c r="G83" s="4"/>
-      <c r="H83" s="4"/>
+      <c r="G83" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="I83" s="7"/>
-      <c r="J83" s="7"/>
+      <c r="J83" s="8" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A84" s="4"/>
-      <c r="B84" s="5"/>
+      <c r="A84" s="4">
+        <v>81</v>
+      </c>
+      <c r="B84" s="5">
+        <v>44466</v>
+      </c>
       <c r="C84" s="6"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
+      <c r="D84" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F84" s="4"/>
-      <c r="G84" s="4"/>
-      <c r="H84" s="4"/>
+      <c r="G84" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="I84" s="7"/>
-      <c r="J84" s="7"/>
+      <c r="J84" s="8" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A85" s="4"/>
-      <c r="B85" s="5"/>
+      <c r="A85" s="4">
+        <v>82</v>
+      </c>
+      <c r="B85" s="5">
+        <v>44494</v>
+      </c>
       <c r="C85" s="6"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="4"/>
+      <c r="D85" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F85" s="4"/>
-      <c r="G85" s="4"/>
-      <c r="H85" s="4"/>
+      <c r="G85" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="I85" s="7"/>
-      <c r="J85" s="7"/>
+      <c r="J85" s="8" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A86" s="4"/>
-      <c r="B86" s="5"/>
+      <c r="A86" s="4">
+        <v>83</v>
+      </c>
+      <c r="B86" s="5">
+        <v>44505</v>
+      </c>
       <c r="C86" s="6"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
+      <c r="D86" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F86" s="4"/>
-      <c r="G86" s="4"/>
-      <c r="H86" s="4"/>
+      <c r="G86" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="I86" s="7"/>
-      <c r="J86" s="7"/>
+      <c r="J86" s="8" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A87" s="4"/>
-      <c r="B87" s="5"/>
+      <c r="A87" s="4">
+        <v>84</v>
+      </c>
+      <c r="B87" s="5">
+        <v>44509</v>
+      </c>
       <c r="C87" s="6"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
+      <c r="D87" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F87" s="4"/>
-      <c r="G87" s="4"/>
-      <c r="H87" s="4"/>
+      <c r="G87" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="I87" s="7"/>
-      <c r="J87" s="7"/>
+      <c r="J87" s="8" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A88" s="4"/>
-      <c r="B88" s="5"/>
+      <c r="A88" s="4">
+        <v>85</v>
+      </c>
+      <c r="B88" s="5">
+        <v>44519</v>
+      </c>
       <c r="C88" s="6"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
+      <c r="D88" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F88" s="4"/>
-      <c r="G88" s="4"/>
-      <c r="H88" s="4"/>
+      <c r="G88" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="I88" s="7"/>
-      <c r="J88" s="7"/>
+      <c r="J88" s="8" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A89" s="4"/>
-      <c r="B89" s="5"/>
+      <c r="A89" s="4">
+        <v>86</v>
+      </c>
+      <c r="B89" s="5">
+        <v>44519</v>
+      </c>
       <c r="C89" s="6"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
+      <c r="D89" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F89" s="4"/>
-      <c r="G89" s="4"/>
-      <c r="H89" s="4"/>
+      <c r="G89" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="I89" s="7"/>
-      <c r="J89" s="7"/>
+      <c r="J89" s="8" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A90" s="4"/>
-      <c r="B90" s="5"/>
+      <c r="A90" s="4">
+        <v>87</v>
+      </c>
+      <c r="B90" s="5">
+        <v>44546</v>
+      </c>
       <c r="C90" s="6"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
+      <c r="D90" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F90" s="4"/>
-      <c r="G90" s="4"/>
-      <c r="H90" s="4"/>
+      <c r="G90" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="I90" s="7"/>
-      <c r="J90" s="7"/>
+      <c r="J90" s="8" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A91" s="4"/>
-      <c r="B91" s="5"/>
+      <c r="A91" s="4">
+        <v>88</v>
+      </c>
+      <c r="B91" s="5">
+        <v>44558</v>
+      </c>
       <c r="C91" s="6"/>
-      <c r="D91" s="4"/>
-      <c r="E91" s="4"/>
+      <c r="D91" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F91" s="4"/>
-      <c r="G91" s="4"/>
-      <c r="H91" s="4"/>
+      <c r="G91" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="I91" s="7"/>
-      <c r="J91" s="7"/>
+      <c r="J91" s="8" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="4"/>
@@ -13375,10 +13789,28 @@
     <hyperlink ref="J55" r:id="rId42" xr:uid="{A279FAA2-98D8-438D-AE9A-EE0688D6A2AA}"/>
     <hyperlink ref="J54" r:id="rId43" xr:uid="{91ABD0F5-EC16-4720-ADA2-328255DAE095}"/>
     <hyperlink ref="J53" r:id="rId44" xr:uid="{4A1C2752-81C2-4BC2-9F4F-C2573E2624CF}"/>
+    <hyperlink ref="J91" r:id="rId45" xr:uid="{DA0AD36B-6295-40E6-B99D-F3223E0F9BA6}"/>
+    <hyperlink ref="J90" r:id="rId46" xr:uid="{942043B2-714B-42BF-9F92-2E0D15A91534}"/>
+    <hyperlink ref="J89" r:id="rId47" xr:uid="{936DB5AE-E5E4-4366-B9F4-F00206C9D013}"/>
+    <hyperlink ref="J85:J88" r:id="rId48" display="https://thefreechart.com/x/ro5q4bK0/" xr:uid="{3CF4FC10-B88A-4E95-951A-A1D6A2422748}"/>
+    <hyperlink ref="J84" r:id="rId49" xr:uid="{E2523A11-9970-4926-B2F2-2E90F441E8E4}"/>
+    <hyperlink ref="J83" r:id="rId50" xr:uid="{3EDADFE6-B3DA-4475-8123-581E036CD70C}"/>
+    <hyperlink ref="J82" r:id="rId51" xr:uid="{C4509B63-DC50-4D32-A016-A50F765F170C}"/>
+    <hyperlink ref="J81" r:id="rId52" xr:uid="{002E18A1-6778-478F-9D19-7AC69B01D451}"/>
+    <hyperlink ref="J80" r:id="rId53" xr:uid="{65DD0571-A2EA-4951-8213-F505E673D1B0}"/>
+    <hyperlink ref="J76:J79" r:id="rId54" display="https://thefreechart.com/x/TCAlsMHO/" xr:uid="{B9F5DE3E-29FC-4948-96BB-B6CF8C3A465C}"/>
+    <hyperlink ref="J75" r:id="rId55" xr:uid="{D1F31316-6BE6-4E39-A593-9F7EBFFDBBF2}"/>
+    <hyperlink ref="J72:J74" r:id="rId56" display="https://thefreechart.com/x/z6CZzxXc/" xr:uid="{55DF0909-8396-4595-B64E-EE8BE3D4CD5C}"/>
+    <hyperlink ref="J71" r:id="rId57" xr:uid="{D074F0A6-22C9-4925-865A-06ACDB6890F7}"/>
+    <hyperlink ref="J70" r:id="rId58" xr:uid="{4DFCED91-CAB5-48F7-BFEA-89A63C7DA4FF}"/>
+    <hyperlink ref="J69" r:id="rId59" xr:uid="{6DB2DBCE-BFAD-4A92-BA8F-10129EAFC50F}"/>
+    <hyperlink ref="J66:J68" r:id="rId60" display="https://thefreechart.com/x/qO7A2fVp/" xr:uid="{6BF73598-EAAC-4641-906C-028E3D462163}"/>
+    <hyperlink ref="J64" r:id="rId61" xr:uid="{A3ADB6A9-A40F-44B1-94D4-46A58395C8AA}"/>
+    <hyperlink ref="J65" r:id="rId62" xr:uid="{34FDEFC2-A8D2-4A91-A956-F7C948CDFAF3}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart r:id="rId45"/>
+    <tablePart r:id="rId63"/>
   </tableParts>
 </worksheet>
 </file>